--- a/Input_Data_Sheets/LULC_parameters.xlsx
+++ b/Input_Data_Sheets/LULC_parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcu\Documents\GitHub\HydroPol2D\Input_Data_Sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mngomes/Documents/GitHub/HydroPol2D/Input_Data_Sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D39B3B-96FB-4922-A99F-E32AE5FB2831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B26F66-8CF2-5044-93D2-26FA60966CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LULC_parameters" sheetId="1" r:id="rId1"/>
@@ -144,7 +144,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t xml:space="preserve">HydroPol2D - LULC Parameters </t>
   </si>
@@ -248,52 +248,37 @@
     <t>index_impervious</t>
   </si>
   <si>
-    <t>Open Water</t>
-  </si>
-  <si>
-    <t>Developed, Open Space</t>
-  </si>
-  <si>
-    <t>Developed, Low Intensity</t>
-  </si>
-  <si>
-    <t>Developed, Medium Intensity</t>
-  </si>
-  <si>
-    <t>Developed, High Intensity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	Barren Land (Rock/Sand/Clay)</t>
-  </si>
-  <si>
-    <t>Deciduous Forest</t>
-  </si>
-  <si>
-    <t>Evergreen Forest</t>
-  </si>
-  <si>
-    <t>Mixed Forest</t>
-  </si>
-  <si>
-    <t>Shrub/Scrub</t>
-  </si>
-  <si>
-    <t>Grassland/Herbaceous</t>
-  </si>
-  <si>
-    <t>Pasture/Hay</t>
-  </si>
-  <si>
-    <t>Cultivated Crops</t>
-  </si>
-  <si>
-    <t>Woody Wetlands</t>
-  </si>
-  <si>
-    <t>Emergent Herbaceous Wetlands</t>
-  </si>
-  <si>
-    <t>Synthetic_LULC</t>
+    <t>Tree cover</t>
+  </si>
+  <si>
+    <t>Shrubland</t>
+  </si>
+  <si>
+    <t>Grassland</t>
+  </si>
+  <si>
+    <t>Cropland</t>
+  </si>
+  <si>
+    <t>Built-up</t>
+  </si>
+  <si>
+    <t>Bare / sparse vegetation</t>
+  </si>
+  <si>
+    <t>Snow and ice</t>
+  </si>
+  <si>
+    <t>Permanent water bodies</t>
+  </si>
+  <si>
+    <t>Herbaceous wetland</t>
+  </si>
+  <si>
+    <t>Mangroves</t>
+  </si>
+  <si>
+    <t>Moss and lichen</t>
   </si>
 </sst>
 </file>
@@ -715,23 +700,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K48"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="20.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.1640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.33203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="6" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.85546875" style="1"/>
+    <col min="12" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -746,7 +731,7 @@
       <c r="J1" s="9"/>
       <c r="K1" s="10"/>
     </row>
-    <row r="2" spans="1:11" ht="20.25" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -779,15 +764,15 @@
       </c>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4">
-        <v>3.5000000000000003E-2</v>
+        <v>0.1</v>
       </c>
       <c r="D3" s="5">
         <v>0</v>
@@ -796,31 +781,31 @@
         <v>0</v>
       </c>
       <c r="F3" s="4">
-        <v>5.72</v>
+        <v>10</v>
       </c>
       <c r="G3" s="4">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="H3" s="4">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="I3" s="4">
         <v>1.2</v>
       </c>
       <c r="J3" s="6">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="K3" s="3"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" s="4">
-        <v>3.5000000000000003E-2</v>
+        <v>0.08</v>
       </c>
       <c r="D4" s="5">
         <v>0</v>
@@ -829,13 +814,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="4">
-        <v>5.72</v>
+        <v>12</v>
       </c>
       <c r="G4" s="4">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="H4" s="4">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="I4" s="4">
         <v>1.2</v>
@@ -843,15 +828,15 @@
       <c r="J4" s="6"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="4">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C5" s="4">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="D5" s="5">
         <v>0</v>
@@ -860,13 +845,13 @@
         <v>0</v>
       </c>
       <c r="F5" s="4">
-        <v>5.72</v>
+        <v>15</v>
       </c>
       <c r="G5" s="4">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="H5" s="4">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="I5" s="4">
         <v>1.2</v>
@@ -874,15 +859,15 @@
       <c r="J5" s="6"/>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="4">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C6" s="4">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="D6" s="5">
         <v>0</v>
@@ -891,29 +876,29 @@
         <v>0</v>
       </c>
       <c r="F6" s="4">
-        <v>5.72</v>
+        <v>30</v>
       </c>
       <c r="G6" s="4">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H6" s="4">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="I6" s="4">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="4">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="C7" s="4">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="D7" s="5">
         <v>0</v>
@@ -922,29 +907,29 @@
         <v>0</v>
       </c>
       <c r="F7" s="4">
-        <v>5.72</v>
+        <v>80</v>
       </c>
       <c r="G7" s="4">
-        <v>0.17</v>
+        <v>0.3</v>
       </c>
       <c r="H7" s="4">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="I7" s="4">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="4">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="C8" s="4">
-        <v>0.03</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="D8" s="5">
         <v>0</v>
@@ -953,60 +938,60 @@
         <v>0</v>
       </c>
       <c r="F8" s="4">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="G8" s="4">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H8" s="4">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="I8" s="4">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="4">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="C9" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4">
         <v>0.1</v>
       </c>
-      <c r="D9" s="5">
-        <v>0</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4">
-        <v>27</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0.17</v>
-      </c>
       <c r="H9" s="4">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="I9" s="4">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="4">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="C10" s="4">
-        <v>0.15</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="D10" s="5">
         <v>0</v>
@@ -1015,26 +1000,26 @@
         <v>0</v>
       </c>
       <c r="F10" s="4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="I10" s="4">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="3"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="4">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="C11" s="4">
         <v>0.12</v>
@@ -1046,13 +1031,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="4">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="G11" s="4">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H11" s="4">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="I11" s="4">
         <v>1.2</v>
@@ -1060,15 +1045,15 @@
       <c r="J11" s="6"/>
       <c r="K11" s="3"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B12" s="4">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="C12" s="4">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="D12" s="5">
         <v>0</v>
@@ -1077,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="4">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="G12" s="4">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H12" s="4">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="I12" s="4">
         <v>1.2</v>
@@ -1091,15 +1076,15 @@
       <c r="J12" s="6"/>
       <c r="K12" s="3"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B13" s="4">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="C13" s="4">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="D13" s="5">
         <v>0</v>
@@ -1108,176 +1093,86 @@
         <v>0</v>
       </c>
       <c r="F13" s="4">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="G13" s="4">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H13" s="4">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="I13" s="4">
-        <v>1.2</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="3"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="4">
-        <v>81</v>
-      </c>
-      <c r="C14" s="4">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="D14" s="5">
-        <v>0</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4">
-        <v>27</v>
-      </c>
-      <c r="G14" s="4">
-        <v>0.17</v>
-      </c>
-      <c r="H14" s="4">
-        <v>1200</v>
-      </c>
-      <c r="I14" s="4">
-        <v>1.2</v>
-      </c>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
       <c r="J14" s="6"/>
       <c r="K14" s="3"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="4">
-        <v>82</v>
-      </c>
-      <c r="C15" s="4">
-        <v>0.05</v>
-      </c>
-      <c r="D15" s="5">
-        <v>0</v>
-      </c>
-      <c r="E15" s="4">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4">
-        <v>27</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0.17</v>
-      </c>
-      <c r="H15" s="4">
-        <v>1200</v>
-      </c>
-      <c r="I15" s="4">
-        <v>1.2</v>
-      </c>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
       <c r="J15" s="6"/>
       <c r="K15" s="3"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="4">
-        <v>90</v>
-      </c>
-      <c r="C16" s="4">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="D16" s="5">
-        <v>0</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4">
-        <v>27</v>
-      </c>
-      <c r="G16" s="4">
-        <v>0.17</v>
-      </c>
-      <c r="H16" s="4">
-        <v>1200</v>
-      </c>
-      <c r="I16" s="4">
-        <v>1.2</v>
-      </c>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
       <c r="J16" s="6"/>
       <c r="K16" s="3"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="4">
-        <v>95</v>
-      </c>
-      <c r="C17" s="4">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="D17" s="5">
-        <v>0</v>
-      </c>
-      <c r="E17" s="4">
-        <v>0</v>
-      </c>
-      <c r="F17" s="4">
-        <v>27</v>
-      </c>
-      <c r="G17" s="4">
-        <v>0.17</v>
-      </c>
-      <c r="H17" s="4">
-        <v>1200</v>
-      </c>
-      <c r="I17" s="4">
-        <v>1.2</v>
-      </c>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
       <c r="J17" s="6"/>
       <c r="K17" s="3"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="4">
-        <v>1</v>
-      </c>
-      <c r="C18" s="4">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4">
-        <v>27</v>
-      </c>
-      <c r="G18" s="4">
-        <v>0.17</v>
-      </c>
-      <c r="H18" s="4">
-        <v>1200</v>
-      </c>
-      <c r="I18" s="4">
-        <v>1.2</v>
-      </c>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
       <c r="J18" s="6"/>
       <c r="K18" s="3"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -1290,7 +1185,7 @@
       <c r="J19" s="6"/>
       <c r="K19" s="3"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -1303,7 +1198,7 @@
       <c r="J20" s="6"/>
       <c r="K20" s="3"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1316,7 +1211,7 @@
       <c r="J21" s="6"/>
       <c r="K21" s="3"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1329,7 +1224,7 @@
       <c r="J22" s="6"/>
       <c r="K22" s="3"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1342,7 +1237,7 @@
       <c r="J23" s="6"/>
       <c r="K23" s="3"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1355,7 +1250,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="3"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1368,7 +1263,7 @@
       <c r="J25" s="6"/>
       <c r="K25" s="3"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1381,7 +1276,7 @@
       <c r="J26" s="6"/>
       <c r="K26" s="3"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1394,7 +1289,7 @@
       <c r="J27" s="6"/>
       <c r="K27" s="3"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1407,7 +1302,7 @@
       <c r="J28" s="6"/>
       <c r="K28" s="3"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -1420,7 +1315,7 @@
       <c r="J29" s="6"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -1433,7 +1328,7 @@
       <c r="J30" s="6"/>
       <c r="K30" s="3"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -1446,7 +1341,7 @@
       <c r="J31" s="6"/>
       <c r="K31" s="3"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -1459,7 +1354,7 @@
       <c r="J32" s="6"/>
       <c r="K32" s="3"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -1472,7 +1367,7 @@
       <c r="J33" s="6"/>
       <c r="K33" s="3"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -1485,7 +1380,7 @@
       <c r="J34" s="6"/>
       <c r="K34" s="3"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1498,7 +1393,7 @@
       <c r="J35" s="6"/>
       <c r="K35" s="3"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -1511,7 +1406,7 @@
       <c r="J36" s="6"/>
       <c r="K36" s="3"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -1524,7 +1419,7 @@
       <c r="J37" s="6"/>
       <c r="K37" s="3"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -1537,7 +1432,7 @@
       <c r="J38" s="6"/>
       <c r="K38" s="3"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -1550,7 +1445,7 @@
       <c r="J39" s="6"/>
       <c r="K39" s="3"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -1563,7 +1458,7 @@
       <c r="J40" s="6"/>
       <c r="K40" s="3"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -1576,7 +1471,7 @@
       <c r="J41" s="6"/>
       <c r="K41" s="3"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -1589,7 +1484,7 @@
       <c r="J42" s="6"/>
       <c r="K42" s="3"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -1602,7 +1497,7 @@
       <c r="J43" s="6"/>
       <c r="K43" s="3"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -1615,7 +1510,7 @@
       <c r="J44" s="6"/>
       <c r="K44" s="3"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -1628,7 +1523,7 @@
       <c r="J45" s="6"/>
       <c r="K45" s="3"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -1641,7 +1536,7 @@
       <c r="J46" s="6"/>
       <c r="K46" s="3"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -1654,7 +1549,7 @@
       <c r="J47" s="6"/>
       <c r="K47" s="3"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
